--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2024_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2024_los_rios.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:07</t>
+    <t xml:space="preserve">2026-09-24 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -567,13 +567,13 @@
         <v>12</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +590,13 @@
         <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.27</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -613,13 +613,13 @@
         <v>12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>12</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +659,13 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -935,13 +935,13 @@
         <v>12</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="19">
@@ -958,13 +958,13 @@
         <v>12</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="20">
@@ -981,13 +981,13 @@
         <v>12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="21">
@@ -1004,13 +1004,13 @@
         <v>12</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="22">
@@ -1027,13 +1027,13 @@
         <v>12</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
@@ -1050,13 +1050,13 @@
         <v>12</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
